--- a/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791D3D7F-B0C4-41E7-B5A1-957587ECD7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DEFBDF-344D-47FF-856E-72257C277C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,66 +31,197 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+  <si>
+    <t>Effects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧之血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>资源标识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>效果</t>
-  </si>
-  <si>
-    <t>Effects</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardEffectEntry[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IconKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>稀有度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealOnCombatEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"amount":6}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在战斗结束时，回复6点生命。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗之血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"amount":12}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在战斗结束时，回复12点生命。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红头骨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你的生命值低于或等于50%时，你额外获得3点力量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纸蛙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有易伤状态的敌人受到的伤害增加75%而非50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自成型黏土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你在战斗中失去生命，就在下一回合获得3点格挡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡戎之灰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你消耗一张牌，对所有敌人造成3点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔之舌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合第一次在回合内失去生命值时，回复等量的生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>损毁头盔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你在每场战斗中第一次获得的力量值翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫磺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你的每个回合开始时，你获得2点力量，所有敌人获得1点力量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThresholdStrength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"threshold":0.5,"strength":3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyVulnerableMultiplier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"multiplier":1.75}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlockOnHpLossNextTurn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"block":3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageOnExhaust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"damage":3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealOnFirstHpLoss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleFirstStrength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrengthOnTurnStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"playerStrength":2,"enemyStrength":1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -630,94 +761,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="45.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DEFBDF-344D-47FF-856E-72257C277C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BE28EA-03A7-4976-87AA-AFC5050504B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,6 +240,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -867,7 +868,9 @@
         <v>19</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
@@ -886,7 +889,9 @@
         <v>22</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
@@ -905,7 +910,9 @@
         <v>24</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>38</v>
       </c>
@@ -924,7 +931,9 @@
         <v>26</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
@@ -943,7 +952,9 @@
         <v>28</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
@@ -962,7 +973,9 @@
         <v>30</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>44</v>
       </c>
@@ -979,7 +992,9 @@
         <v>32</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>45</v>
       </c>
@@ -996,7 +1011,9 @@
         <v>34</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
       </c>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BE28EA-03A7-4976-87AA-AFC5050504B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F2764B-190E-49A7-9888-D59956B50FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Effects</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -223,6 +223,33 @@
   <si>
     <t>{"playerStrength":2,"enemyStrength":1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burning_blood</t>
+  </si>
+  <si>
+    <t>black_blood</t>
+  </si>
+  <si>
+    <t>red_skull</t>
+  </si>
+  <si>
+    <t>paper_phrog</t>
+  </si>
+  <si>
+    <t>self_forming_clay</t>
+  </si>
+  <si>
+    <t>charons_ashes</t>
+  </si>
+  <si>
+    <t>demon_tongue</t>
+  </si>
+  <si>
+    <t>ruined_helmet</t>
+  </si>
+  <si>
+    <t>brimstone</t>
   </si>
 </sst>
 </file>
@@ -846,7 +873,9 @@
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
@@ -867,7 +896,9 @@
       <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
@@ -888,7 +919,9 @@
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
@@ -909,7 +942,9 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
@@ -930,7 +965,9 @@
       <c r="B8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
@@ -951,7 +988,9 @@
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
@@ -972,7 +1011,9 @@
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
@@ -991,7 +1032,9 @@
       <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
@@ -1010,7 +1053,9 @@
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F2764B-190E-49A7-9888-D59956B50FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RelicConfig" sheetId="1" r:id="rId1"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F2764B-190E-49A7-9888-D59956B50FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97144BB-7141-40E2-9B5B-1B7399689FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4212" yWindow="4212" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RelicConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>Effects</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>brimstone</t>
+  </si>
+  <si>
+    <t>HealOnCombatEnd</t>
   </si>
 </sst>
 </file>
@@ -880,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>15</v>
